--- a/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-service-request.xlsx
+++ b/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-service-request.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.5.0</t>
+    <t>1.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-10T06:36:19+00:00</t>
+    <t>2026-08-28T11:20:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -4947,7 +4947,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
         <v>231</v>
       </c>
@@ -5064,7 +5064,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>241</v>
       </c>
@@ -6938,7 +6938,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
         <v>378</v>
       </c>
@@ -7519,7 +7519,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
         <v>402</v>
       </c>
@@ -8106,7 +8106,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
         <v>411</v>
       </c>
@@ -8223,7 +8223,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
         <v>413</v>
       </c>
@@ -8572,7 +8572,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
         <v>416</v>
       </c>
@@ -10779,12 +10779,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AO74">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-service-request.xlsx
+++ b/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-service-request.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.6.0</t>
+    <t>1.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T11:20:46+00:00</t>
+    <t>2026-08-28T12:05:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-service-request.xlsx
+++ b/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-service-request.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.5.0</t>
+    <t>1.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:05:03+00:00</t>
+    <t>2026-08-28T12:17:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>88</v>

--- a/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-service-request.xlsx
+++ b/DiagnosticReportIG/CurrentBuild/StructureDefinition-nilar-service-request.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:17:39+00:00</t>
+    <t>2026-08-31T14:07:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
